--- a/气象/蒙古气象/蒙古低温收集 & 东亚极端冷月均温排名.xlsx
+++ b/气象/蒙古气象/蒙古低温收集 & 东亚极端冷月均温排名.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\蒙古气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746A54F3-221F-4CE8-9D6E-B33804DAAFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D420923-6D49-406E-BC90-1EFC6AAC0AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{237916A9-0E72-4A8C-88B8-0F539FC0B012}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="寒冷爆发力" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">蒙古冷站!$A$2:$E$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">蒙古冷站!$A$2:$G$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2414" uniqueCount="2000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="2003">
   <si>
     <t>undefined</t>
   </si>
@@ -6554,15 +6554,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>早8点后实际最低
--46.0 ~ -46.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2018-01-26(?)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>交换站记录 -49.8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6571,62 +6562,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>实时追踪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>东戈壁气象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蒙古气象官方FB号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">蒙古站点低温收集(部分)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="2" tint="-0.499984740745262"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>蒙古气象不更新早8点之后的低温，表中有些低温不是当天最低</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="2" tint="-0.499984740745262"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>表中站点全部位于定居点，e.g. 东戈壁人口2792，uvs特斯人口5223</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>苏木</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6676,18 +6611,6 @@
     <t>库苏古尔</t>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;= -50; 2018-01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2022;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>扎布汗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6717,6 +6640,55 @@
   </si>
   <si>
     <t>巴彦特斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;= -50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>东戈壁气象FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙古气象FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-46.0 ~ -46.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>date uncertain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>date speculated out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mentioned mostly on 12.26
+Actaully should be 12.27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙古极端低温记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6724,15 +6696,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="0.0_ "/>
     <numFmt numFmtId="179" formatCode="0_ "/>
     <numFmt numFmtId="180" formatCode="#\ ???/???"/>
-    <numFmt numFmtId="181" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="61" x14ac:knownFonts="1">
+  <fonts count="62" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6820,24 +6791,6 @@
       <b/>
       <sz val="24"/>
       <color rgb="FFFFC000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="0" tint="-0.34998626667073579"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="32"/>
-      <color rgb="FF00B0F0"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -7254,8 +7207,8 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="2" tint="-0.499984740745262"/>
+      <sz val="14"/>
+      <color theme="0"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -7263,15 +7216,42 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="10"/>
       <color theme="0"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF92D050"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7395,12 +7375,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFD0363"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7566,7 +7540,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7648,55 +7622,55 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="15" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="15" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="15" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="15" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="18" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="16" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="19" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="17" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="18" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="18" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="18" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="18" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="19" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="20" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="22" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="24" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7708,28 +7682,52 @@
     <xf numFmtId="178" fontId="2" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="18" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7738,34 +7736,10 @@
     <xf numFmtId="0" fontId="33" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="23" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="42" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="40" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="8" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7774,19 +7748,19 @@
     <xf numFmtId="178" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="178" fontId="42" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="44" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="46" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="45" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="47" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="47" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="45" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7795,109 +7769,130 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="48" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="46" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="48" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="46" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="49" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="47" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="50" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="15" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="13" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="178" fontId="57" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="55" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="179" fontId="23" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="21" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
     </xf>
-    <xf numFmtId="179" fontId="23" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="21" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
     </xf>
-    <xf numFmtId="179" fontId="23" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="21" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
     </xf>
-    <xf numFmtId="179" fontId="23" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="21" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
     </xf>
-    <xf numFmtId="179" fontId="23" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="21" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
     </xf>
-    <xf numFmtId="179" fontId="23" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="21" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="6"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="60" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="58" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="58" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="22" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7909,28 +7904,28 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7948,10 +7943,10 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7978,15 +7973,15 @@
   <colors>
     <mruColors>
       <color rgb="FF4CC9F0"/>
-      <color rgb="FF3F37C9"/>
+      <color rgb="FF3A0CA3"/>
+      <color rgb="FFF72585"/>
       <color rgb="FF560BAD"/>
       <color rgb="FFFD0363"/>
+      <color rgb="FF3F37C9"/>
       <color rgb="FFCC095D"/>
       <color rgb="FF9C1057"/>
       <color rgb="FF6B1650"/>
       <color rgb="FF3B1D4A"/>
-      <color rgb="FF0A2344"/>
-      <color rgb="FF3A0CA3"/>
     </mruColors>
   </colors>
   <extLst>
@@ -8310,15 +8305,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="80" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="111"/>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="113"/>
+      <c r="A1" s="118"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="120"/>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
@@ -31899,1432 +31894,1975 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94ABDC8A-163A-480F-B2C9-0CD0B852C7D7}">
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr defaultRowHeight="30" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" style="107" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="96" customWidth="1"/>
     <col min="2" max="2" width="22.59765625" style="24" customWidth="1"/>
-    <col min="3" max="3" width="17.59765625" style="26" customWidth="1"/>
-    <col min="4" max="4" width="23.59765625" style="25" customWidth="1"/>
-    <col min="5" max="5" width="24.59765625" style="99" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="23"/>
+    <col min="3" max="3" width="20.59765625" style="26" customWidth="1"/>
+    <col min="4" max="4" width="10.59765625" style="97" customWidth="1"/>
+    <col min="5" max="6" width="7.59765625" style="97" customWidth="1"/>
+    <col min="7" max="7" width="24.59765625" style="93" customWidth="1"/>
+    <col min="8" max="16384" width="9.06640625" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="108" t="s">
+    <row r="1" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="116" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="95" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="111" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B2" s="112" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C2" s="105" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D2" s="113" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E2" s="114" t="s">
+        <v>2001</v>
+      </c>
+      <c r="F2" s="115" t="s">
+        <v>2002</v>
+      </c>
+      <c r="G2" s="94" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B3" s="108" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C3" s="106">
+        <v>-55.6</v>
+      </c>
+      <c r="D3" s="102">
+        <v>1966</v>
+      </c>
+      <c r="E3" s="103">
+        <v>12</v>
+      </c>
+      <c r="F3" s="104">
+        <v>27</v>
+      </c>
+      <c r="G3" s="100" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B4" s="109" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C4" s="106">
+        <v>-53</v>
+      </c>
+      <c r="D4" s="102">
+        <v>1969</v>
+      </c>
+      <c r="E4" s="103">
+        <v>1</v>
+      </c>
+      <c r="F4" s="104">
+        <v>31</v>
+      </c>
+      <c r="G4" s="98"/>
+    </row>
+    <row r="5" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B5" s="108" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C5" s="106">
+        <v>-55.3</v>
+      </c>
+      <c r="D5" s="102">
+        <v>1976</v>
+      </c>
+      <c r="E5" s="103">
+        <v>12</v>
+      </c>
+      <c r="F5" s="104">
+        <v>31</v>
+      </c>
+      <c r="G5" s="98"/>
+    </row>
+    <row r="6" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="107" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B6" s="109" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C6" s="106">
+        <v>-34.200000000000003</v>
+      </c>
+      <c r="D6" s="102">
+        <v>1993</v>
+      </c>
+      <c r="E6" s="103">
+        <v>4</v>
+      </c>
+      <c r="F6" s="104">
+        <v>5</v>
+      </c>
+      <c r="G6" s="98"/>
+    </row>
+    <row r="7" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="107" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B7" s="109" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C7" s="106">
+        <v>-34.200000000000003</v>
+      </c>
+      <c r="D7" s="102">
+        <v>1993</v>
+      </c>
+      <c r="E7" s="103">
+        <v>4</v>
+      </c>
+      <c r="F7" s="104">
+        <v>6</v>
+      </c>
+      <c r="G7" s="98"/>
+    </row>
+    <row r="8" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="107" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B8" s="109" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C8" s="106">
+        <v>-34</v>
+      </c>
+      <c r="D8" s="102">
+        <v>1993</v>
+      </c>
+      <c r="E8" s="103">
+        <v>4</v>
+      </c>
+      <c r="F8" s="104">
+        <v>7</v>
+      </c>
+      <c r="G8" s="98"/>
+    </row>
+    <row r="9" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="107" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B9" s="109" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C9" s="106">
+        <v>-30</v>
+      </c>
+      <c r="D9" s="102">
+        <v>1993</v>
+      </c>
+      <c r="E9" s="103">
+        <v>4</v>
+      </c>
+      <c r="F9" s="104">
+        <v>8</v>
+      </c>
+      <c r="G9" s="98"/>
+    </row>
+    <row r="10" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="107" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B10" s="110" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C10" s="106">
+        <v>-30.2</v>
+      </c>
+      <c r="D10" s="102">
+        <v>1996</v>
+      </c>
+      <c r="E10" s="103">
+        <v>4</v>
+      </c>
+      <c r="F10" s="104">
+        <v>7</v>
+      </c>
+      <c r="G10" s="98"/>
+    </row>
+    <row r="11" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="107" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B11" s="110" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C11" s="106">
+        <v>-50.4</v>
+      </c>
+      <c r="D11" s="102">
+        <v>2000</v>
+      </c>
+      <c r="E11" s="103">
+        <v>1</v>
+      </c>
+      <c r="F11" s="104">
+        <v>6</v>
+      </c>
+      <c r="G11" s="98"/>
+    </row>
+    <row r="12" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B12" s="109" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C12" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D12" s="102">
+        <v>2001</v>
+      </c>
+      <c r="E12" s="103">
+        <v>1</v>
+      </c>
+      <c r="F12" s="104">
+        <v>8</v>
+      </c>
+      <c r="G12" s="98"/>
+    </row>
+    <row r="13" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B13" s="108" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C13" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D13" s="102">
+        <v>2005</v>
+      </c>
+      <c r="E13" s="103">
+        <v>2</v>
+      </c>
+      <c r="F13" s="104">
+        <v>6</v>
+      </c>
+      <c r="G13" s="98"/>
+    </row>
+    <row r="14" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B14" s="108" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C14" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D14" s="102">
+        <v>2005</v>
+      </c>
+      <c r="E14" s="103">
+        <v>2</v>
+      </c>
+      <c r="F14" s="104">
+        <v>7</v>
+      </c>
+      <c r="G14" s="98"/>
+    </row>
+    <row r="15" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B15" s="108" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C15" s="106">
+        <v>-50.1</v>
+      </c>
+      <c r="D15" s="102">
+        <v>2005</v>
+      </c>
+      <c r="E15" s="103">
+        <v>2</v>
+      </c>
+      <c r="F15" s="104">
+        <v>8</v>
+      </c>
+      <c r="G15" s="98"/>
+    </row>
+    <row r="16" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B16" s="108" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C16" s="106">
+        <v>-50.5</v>
+      </c>
+      <c r="D16" s="102">
+        <v>2005</v>
+      </c>
+      <c r="E16" s="103">
+        <v>2</v>
+      </c>
+      <c r="F16" s="104">
+        <v>9</v>
+      </c>
+      <c r="G16" s="98"/>
+    </row>
+    <row r="17" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B17" s="108" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C17" s="106">
+        <v>-49.7</v>
+      </c>
+      <c r="D17" s="102">
+        <v>2005</v>
+      </c>
+      <c r="E17" s="103">
+        <v>2</v>
+      </c>
+      <c r="F17" s="104">
+        <v>10</v>
+      </c>
+      <c r="G17" s="98"/>
+    </row>
+    <row r="18" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B18" s="108" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C18" s="106">
+        <v>-50.5</v>
+      </c>
+      <c r="D18" s="102">
+        <v>2005</v>
+      </c>
+      <c r="E18" s="103">
+        <v>2</v>
+      </c>
+      <c r="F18" s="104">
+        <v>18</v>
+      </c>
+      <c r="G18" s="98"/>
+    </row>
+    <row r="19" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B19" s="109" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C19" s="106">
+        <v>-50.4</v>
+      </c>
+      <c r="D19" s="102">
+        <v>2005</v>
+      </c>
+      <c r="E19" s="103">
+        <v>2</v>
+      </c>
+      <c r="F19" s="104">
+        <v>18</v>
+      </c>
+      <c r="G19" s="98"/>
+    </row>
+    <row r="20" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B20" s="109" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C20" s="106">
+        <v>-40</v>
+      </c>
+      <c r="D20" s="102">
+        <v>2005</v>
+      </c>
+      <c r="E20" s="103">
+        <v>3</v>
+      </c>
+      <c r="F20" s="104">
+        <v>17</v>
+      </c>
+      <c r="G20" s="98"/>
+    </row>
+    <row r="21" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B21" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C21" s="106">
+        <v>-53.8</v>
+      </c>
+      <c r="D21" s="102">
+        <v>2006</v>
+      </c>
+      <c r="E21" s="103">
+        <v>1</v>
+      </c>
+      <c r="F21" s="104">
+        <v>4</v>
+      </c>
+      <c r="G21" s="98"/>
+    </row>
+    <row r="22" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B22" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C22" s="106">
+        <v>-54</v>
+      </c>
+      <c r="D22" s="102">
+        <v>2006</v>
+      </c>
+      <c r="E22" s="103">
+        <v>1</v>
+      </c>
+      <c r="F22" s="104">
+        <v>5</v>
+      </c>
+      <c r="G22" s="98"/>
+    </row>
+    <row r="23" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B23" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C23" s="106">
+        <v>-52.1</v>
+      </c>
+      <c r="D23" s="102">
+        <v>2006</v>
+      </c>
+      <c r="E23" s="103">
+        <v>1</v>
+      </c>
+      <c r="F23" s="104">
+        <v>6</v>
+      </c>
+      <c r="G23" s="98"/>
+    </row>
+    <row r="24" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B24" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C24" s="106">
+        <v>-50.2</v>
+      </c>
+      <c r="D24" s="102">
+        <v>2008</v>
+      </c>
+      <c r="E24" s="103">
+        <v>2</v>
+      </c>
+      <c r="F24" s="104">
+        <v>2</v>
+      </c>
+      <c r="G24" s="98"/>
+    </row>
+    <row r="25" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B25" s="108" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C25" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D25" s="102">
+        <v>2010</v>
+      </c>
+      <c r="E25" s="103">
+        <v>2</v>
+      </c>
+      <c r="F25" s="104">
+        <v>12</v>
+      </c>
+      <c r="G25" s="98"/>
+    </row>
+    <row r="26" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B26" s="108" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C26" s="106">
+        <v>-49.9</v>
+      </c>
+      <c r="D26" s="102">
+        <v>2010</v>
+      </c>
+      <c r="E26" s="103">
+        <v>2</v>
+      </c>
+      <c r="F26" s="104">
+        <v>14</v>
+      </c>
+      <c r="G26" s="98"/>
+    </row>
+    <row r="27" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="107" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B27" s="109" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C27" s="106">
+        <v>-34.1</v>
+      </c>
+      <c r="D27" s="102">
+        <v>2010</v>
+      </c>
+      <c r="E27" s="103">
+        <v>4</v>
+      </c>
+      <c r="F27" s="104">
+        <v>12</v>
+      </c>
+      <c r="G27" s="98"/>
+    </row>
+    <row r="28" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B28" s="109" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C28" s="106">
+        <v>-50.2</v>
+      </c>
+      <c r="D28" s="102">
+        <v>2011</v>
+      </c>
+      <c r="E28" s="103">
+        <v>1</v>
+      </c>
+      <c r="F28" s="104">
+        <v>20</v>
+      </c>
+      <c r="G28" s="98"/>
+    </row>
+    <row r="29" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="107" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B29" s="109" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C29" s="106">
+        <v>-50.1</v>
+      </c>
+      <c r="D29" s="102">
+        <v>2011</v>
+      </c>
+      <c r="E29" s="103">
+        <v>1</v>
+      </c>
+      <c r="F29" s="104">
+        <v>23</v>
+      </c>
+      <c r="G29" s="98"/>
+    </row>
+    <row r="30" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B30" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C30" s="106">
+        <v>-50.3</v>
+      </c>
+      <c r="D30" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E30" s="103">
+        <v>1</v>
+      </c>
+      <c r="F30" s="104">
+        <v>18</v>
+      </c>
+      <c r="G30" s="98"/>
+    </row>
+    <row r="31" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B31" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C31" s="106">
+        <v>-50.4</v>
+      </c>
+      <c r="D31" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E31" s="103">
+        <v>1</v>
+      </c>
+      <c r="F31" s="104">
+        <v>23</v>
+      </c>
+      <c r="G31" s="98"/>
+    </row>
+    <row r="32" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B32" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C32" s="106">
+        <v>-53.2</v>
+      </c>
+      <c r="D32" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E32" s="103">
+        <v>1</v>
+      </c>
+      <c r="F32" s="104">
+        <v>25</v>
+      </c>
+      <c r="G32" s="98"/>
+    </row>
+    <row r="33" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B33" s="109" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C33" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D33" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E33" s="103">
+        <v>1</v>
+      </c>
+      <c r="F33" s="104">
+        <v>25</v>
+      </c>
+      <c r="G33" s="98"/>
+    </row>
+    <row r="34" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B34" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C34" s="106">
+        <v>-53</v>
+      </c>
+      <c r="D34" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E34" s="103">
+        <v>1</v>
+      </c>
+      <c r="F34" s="104">
+        <v>26</v>
+      </c>
+      <c r="G34" s="98"/>
+    </row>
+    <row r="35" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B35" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C35" s="106">
+        <v>-53.9</v>
+      </c>
+      <c r="D35" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E35" s="103">
+        <v>1</v>
+      </c>
+      <c r="F35" s="104">
+        <v>27</v>
+      </c>
+      <c r="G35" s="98"/>
+    </row>
+    <row r="36" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B36" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C36" s="106">
+        <v>-55.3</v>
+      </c>
+      <c r="D36" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E36" s="103">
+        <v>1</v>
+      </c>
+      <c r="F36" s="104">
+        <v>28</v>
+      </c>
+      <c r="G36" s="98"/>
+    </row>
+    <row r="37" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B37" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C37" s="106">
+        <v>-54.4</v>
+      </c>
+      <c r="D37" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E37" s="103">
+        <v>1</v>
+      </c>
+      <c r="F37" s="104">
+        <v>29</v>
+      </c>
+      <c r="G37" s="98"/>
+    </row>
+    <row r="38" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B38" s="109" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C38" s="106">
+        <v>-51.9</v>
+      </c>
+      <c r="D38" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E38" s="103">
+        <v>1</v>
+      </c>
+      <c r="F38" s="104">
+        <v>29</v>
+      </c>
+      <c r="G38" s="98"/>
+    </row>
+    <row r="39" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B39" s="108" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C39" s="106">
+        <v>-50.2</v>
+      </c>
+      <c r="D39" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E39" s="103">
+        <v>1</v>
+      </c>
+      <c r="F39" s="104">
+        <v>29</v>
+      </c>
+      <c r="G39" s="98"/>
+    </row>
+    <row r="40" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B40" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C40" s="106">
+        <v>-55</v>
+      </c>
+      <c r="D40" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E40" s="103">
+        <v>1</v>
+      </c>
+      <c r="F40" s="104">
+        <v>30</v>
+      </c>
+      <c r="G40" s="98"/>
+    </row>
+    <row r="41" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B41" s="109" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C41" s="106">
+        <v>-52.8</v>
+      </c>
+      <c r="D41" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E41" s="103">
+        <v>1</v>
+      </c>
+      <c r="F41" s="104">
+        <v>30</v>
+      </c>
+      <c r="G41" s="98"/>
+    </row>
+    <row r="42" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B42" s="108" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C42" s="106">
+        <v>-50.7</v>
+      </c>
+      <c r="D42" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E42" s="103">
+        <v>1</v>
+      </c>
+      <c r="F42" s="104">
+        <v>30</v>
+      </c>
+      <c r="G42" s="98"/>
+    </row>
+    <row r="43" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B43" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C43" s="106">
+        <v>-51.6</v>
+      </c>
+      <c r="D43" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E43" s="103">
+        <v>1</v>
+      </c>
+      <c r="F43" s="104">
+        <v>31</v>
+      </c>
+      <c r="G43" s="98"/>
+    </row>
+    <row r="44" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B44" s="109" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C44" s="106">
+        <v>-51.5</v>
+      </c>
+      <c r="D44" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E44" s="103">
+        <v>1</v>
+      </c>
+      <c r="F44" s="104">
+        <v>31</v>
+      </c>
+      <c r="G44" s="98"/>
+    </row>
+    <row r="45" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B45" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C45" s="106">
+        <v>-50.5</v>
+      </c>
+      <c r="D45" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E45" s="103">
+        <v>2</v>
+      </c>
+      <c r="F45" s="104">
+        <v>1</v>
+      </c>
+      <c r="G45" s="98"/>
+    </row>
+    <row r="46" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B46" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C46" s="106">
+        <v>-50.2</v>
+      </c>
+      <c r="D46" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E46" s="103">
+        <v>2</v>
+      </c>
+      <c r="F46" s="104">
+        <v>3</v>
+      </c>
+      <c r="G46" s="98"/>
+    </row>
+    <row r="47" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B47" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C47" s="106">
+        <v>-53.2</v>
+      </c>
+      <c r="D47" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E47" s="103">
+        <v>2</v>
+      </c>
+      <c r="F47" s="104">
+        <v>4</v>
+      </c>
+      <c r="G47" s="98"/>
+    </row>
+    <row r="48" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B48" s="109" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C48" s="106">
+        <v>-51</v>
+      </c>
+      <c r="D48" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E48" s="103">
+        <v>2</v>
+      </c>
+      <c r="F48" s="104">
+        <v>4</v>
+      </c>
+      <c r="G48" s="98"/>
+    </row>
+    <row r="49" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B49" s="109" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C49" s="106">
+        <v>-52.9</v>
+      </c>
+      <c r="D49" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E49" s="103">
+        <v>2</v>
+      </c>
+      <c r="F49" s="104">
+        <v>5</v>
+      </c>
+      <c r="G49" s="98"/>
+    </row>
+    <row r="50" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B50" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C50" s="106">
+        <v>-52.3</v>
+      </c>
+      <c r="D50" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E50" s="103">
+        <v>2</v>
+      </c>
+      <c r="F50" s="104">
+        <v>5</v>
+      </c>
+      <c r="G50" s="98"/>
+    </row>
+    <row r="51" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B51" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C51" s="106">
+        <v>-53.3</v>
+      </c>
+      <c r="D51" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E51" s="103">
+        <v>2</v>
+      </c>
+      <c r="F51" s="104">
+        <v>6</v>
+      </c>
+      <c r="G51" s="98"/>
+    </row>
+    <row r="52" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B52" s="109" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C52" s="106">
+        <v>-52</v>
+      </c>
+      <c r="D52" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E52" s="103">
+        <v>2</v>
+      </c>
+      <c r="F52" s="104">
+        <v>6</v>
+      </c>
+      <c r="G52" s="98"/>
+    </row>
+    <row r="53" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B53" s="109" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C53" s="106">
+        <v>-54.7</v>
+      </c>
+      <c r="D53" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E53" s="103">
+        <v>2</v>
+      </c>
+      <c r="F53" s="104">
+        <v>12</v>
+      </c>
+      <c r="G53" s="99"/>
+    </row>
+    <row r="54" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B54" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C54" s="106">
+        <v>-53</v>
+      </c>
+      <c r="D54" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E54" s="103">
+        <v>2</v>
+      </c>
+      <c r="F54" s="104">
+        <v>13</v>
+      </c>
+      <c r="G54" s="99"/>
+    </row>
+    <row r="55" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B55" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C55" s="106">
+        <v>-54.2</v>
+      </c>
+      <c r="D55" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E55" s="103">
+        <v>2</v>
+      </c>
+      <c r="F55" s="104">
+        <v>14</v>
+      </c>
+      <c r="G55" s="99"/>
+    </row>
+    <row r="56" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B56" s="109" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C56" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D56" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E56" s="103">
+        <v>2</v>
+      </c>
+      <c r="F56" s="104">
+        <v>15</v>
+      </c>
+      <c r="G56" s="99"/>
+    </row>
+    <row r="57" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B57" s="109" t="s">
         <v>1975</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="102" t="s">
-        <v>1786</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="105" t="s">
+      <c r="C57" s="106">
+        <v>-50.2</v>
+      </c>
+      <c r="D57" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E57" s="103">
+        <v>2</v>
+      </c>
+      <c r="F57" s="104">
+        <v>22</v>
+      </c>
+      <c r="G57" s="99"/>
+    </row>
+    <row r="58" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B58" s="109" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C58" s="106">
+        <v>-51.9</v>
+      </c>
+      <c r="D58" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E58" s="103">
+        <v>2</v>
+      </c>
+      <c r="F58" s="104">
+        <v>23</v>
+      </c>
+      <c r="G58" s="99"/>
+    </row>
+    <row r="59" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B59" s="109" t="s">
         <v>1977</v>
       </c>
-      <c r="B2" s="104" t="s">
-        <v>1976</v>
-      </c>
-      <c r="C2" s="93" t="s">
-        <v>1785</v>
-      </c>
-      <c r="D2" s="93" t="s">
-        <v>1989</v>
-      </c>
-      <c r="E2" s="100"/>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B3" s="94" t="s">
+      <c r="C59" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D59" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E59" s="103">
+        <v>3</v>
+      </c>
+      <c r="F59" s="104">
+        <v>7</v>
+      </c>
+      <c r="G59" s="99"/>
+    </row>
+    <row r="60" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B60" s="109" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C60" s="106">
+        <v>-47.4</v>
+      </c>
+      <c r="D60" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E60" s="103">
+        <v>3</v>
+      </c>
+      <c r="F60" s="104">
+        <v>7</v>
+      </c>
+      <c r="G60" s="99"/>
+    </row>
+    <row r="61" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B61" s="109" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C61" s="106">
+        <v>-50.8</v>
+      </c>
+      <c r="D61" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E61" s="103">
+        <v>3</v>
+      </c>
+      <c r="F61" s="104">
+        <v>8</v>
+      </c>
+      <c r="G61" s="99"/>
+    </row>
+    <row r="62" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B62" s="109" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C62" s="106">
+        <v>-54.2</v>
+      </c>
+      <c r="D62" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E62" s="103">
+        <v>3</v>
+      </c>
+      <c r="F62" s="104">
+        <v>9</v>
+      </c>
+      <c r="G62" s="99"/>
+    </row>
+    <row r="63" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B63" s="109" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C63" s="106">
+        <v>-53</v>
+      </c>
+      <c r="D63" s="102">
+        <v>2016</v>
+      </c>
+      <c r="E63" s="103">
+        <v>3</v>
+      </c>
+      <c r="F63" s="104">
+        <v>10</v>
+      </c>
+      <c r="G63" s="99"/>
+    </row>
+    <row r="64" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B64" s="108" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C64" s="106">
+        <v>-45.4</v>
+      </c>
+      <c r="D64" s="102">
+        <v>2017</v>
+      </c>
+      <c r="E64" s="103">
+        <v>1</v>
+      </c>
+      <c r="F64" s="104">
+        <v>28</v>
+      </c>
+      <c r="G64" s="99"/>
+    </row>
+    <row r="65" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B65" s="109" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C65" s="106">
+        <v>-51.6</v>
+      </c>
+      <c r="D65" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E65" s="103">
+        <v>1</v>
+      </c>
+      <c r="F65" s="104">
+        <v>23</v>
+      </c>
+      <c r="G65" s="99"/>
+    </row>
+    <row r="66" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B66" s="109" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C66" s="106">
+        <v>-51.3</v>
+      </c>
+      <c r="D66" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E66" s="103">
+        <v>1</v>
+      </c>
+      <c r="F66" s="104">
+        <v>23</v>
+      </c>
+      <c r="G66" s="99"/>
+    </row>
+    <row r="67" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B67" s="109" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C67" s="106">
+        <v>-53.2</v>
+      </c>
+      <c r="D67" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E67" s="103">
+        <v>1</v>
+      </c>
+      <c r="F67" s="104">
+        <v>24</v>
+      </c>
+      <c r="G67" s="99"/>
+    </row>
+    <row r="68" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B68" s="109" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C68" s="106">
+        <v>-51.7</v>
+      </c>
+      <c r="D68" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E68" s="103">
+        <v>1</v>
+      </c>
+      <c r="F68" s="104">
+        <v>24</v>
+      </c>
+      <c r="G68" s="99"/>
+    </row>
+    <row r="69" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B69" s="109" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C69" s="106">
+        <v>-50.7</v>
+      </c>
+      <c r="D69" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E69" s="103">
+        <v>1</v>
+      </c>
+      <c r="F69" s="104">
+        <v>25</v>
+      </c>
+      <c r="G69" s="99"/>
+    </row>
+    <row r="70" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B70" s="109" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C70" s="106">
+        <v>-50.3</v>
+      </c>
+      <c r="D70" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E70" s="103">
+        <v>1</v>
+      </c>
+      <c r="F70" s="104">
+        <v>25</v>
+      </c>
+      <c r="G70" s="99"/>
+    </row>
+    <row r="71" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B71" s="109" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C71" s="106">
+        <v>-50.1</v>
+      </c>
+      <c r="D71" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E71" s="103">
+        <v>1</v>
+      </c>
+      <c r="F71" s="104">
+        <v>25</v>
+      </c>
+      <c r="G71" s="99"/>
+    </row>
+    <row r="72" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B72" s="109" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C72" s="106">
+        <v>-50.2</v>
+      </c>
+      <c r="D72" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E72" s="103">
+        <v>1</v>
+      </c>
+      <c r="F72" s="104">
+        <v>26</v>
+      </c>
+      <c r="G72" s="99" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B73" s="108" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C73" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D73" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E73" s="103">
+        <v>1</v>
+      </c>
+      <c r="F73" s="104">
+        <v>26</v>
+      </c>
+      <c r="G73" s="99" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B74" s="108" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C74" s="106">
+        <v>-49.9</v>
+      </c>
+      <c r="D74" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E74" s="103">
+        <v>1</v>
+      </c>
+      <c r="F74" s="104">
+        <v>26</v>
+      </c>
+      <c r="G74" s="99"/>
+    </row>
+    <row r="75" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B75" s="109" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C75" s="106">
+        <v>-51.8</v>
+      </c>
+      <c r="D75" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E75" s="103">
+        <v>1</v>
+      </c>
+      <c r="F75" s="104">
+        <v>27</v>
+      </c>
+      <c r="G75" s="99"/>
+    </row>
+    <row r="76" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B76" s="109" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C76" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D76" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E76" s="103">
+        <v>1</v>
+      </c>
+      <c r="F76" s="104"/>
+      <c r="G76" s="99" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B77" s="109" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C77" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D77" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E77" s="103">
+        <v>1</v>
+      </c>
+      <c r="F77" s="104"/>
+      <c r="G77" s="99" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B78" s="109" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C78" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D78" s="102">
+        <v>2018</v>
+      </c>
+      <c r="E78" s="103">
+        <v>1</v>
+      </c>
+      <c r="F78" s="104"/>
+      <c r="G78" s="99" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B79" s="109" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C79" s="106">
+        <v>-48.4</v>
+      </c>
+      <c r="D79" s="102">
+        <v>2019</v>
+      </c>
+      <c r="E79" s="103">
+        <v>12</v>
+      </c>
+      <c r="F79" s="104">
+        <v>29</v>
+      </c>
+      <c r="G79" s="99"/>
+    </row>
+    <row r="80" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B80" s="109" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C80" s="106">
+        <v>-49.6</v>
+      </c>
+      <c r="D80" s="102">
+        <v>2020</v>
+      </c>
+      <c r="E80" s="103">
+        <v>12</v>
+      </c>
+      <c r="F80" s="104">
+        <v>29</v>
+      </c>
+      <c r="G80" s="99"/>
+    </row>
+    <row r="81" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B81" s="109" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C81" s="106">
+        <v>-47.2</v>
+      </c>
+      <c r="D81" s="102">
+        <v>2021</v>
+      </c>
+      <c r="E81" s="103">
+        <v>1</v>
+      </c>
+      <c r="F81" s="104">
+        <v>4</v>
+      </c>
+      <c r="G81" s="99"/>
+    </row>
+    <row r="82" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B82" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C82" s="106">
+        <v>-46.8</v>
+      </c>
+      <c r="D82" s="102">
+        <v>2022</v>
+      </c>
+      <c r="E82" s="103"/>
+      <c r="F82" s="104"/>
+      <c r="G82" s="99"/>
+    </row>
+    <row r="83" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B83" s="109" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C83" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D83" s="102">
+        <v>2023</v>
+      </c>
+      <c r="E83" s="103">
+        <v>1</v>
+      </c>
+      <c r="F83" s="104">
+        <v>23</v>
+      </c>
+      <c r="G83" s="99" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B84" s="108" t="s">
         <v>1944</v>
       </c>
-      <c r="C3" s="95">
-        <v>-55.6</v>
-      </c>
-      <c r="D3" s="96">
-        <v>24467</v>
-      </c>
-      <c r="E3" s="101"/>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B4" s="94" t="s">
-        <v>1971</v>
-      </c>
-      <c r="C4" s="95">
-        <v>-53</v>
-      </c>
-      <c r="D4" s="96">
-        <v>25234</v>
-      </c>
-      <c r="E4" s="101"/>
-    </row>
-    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B5" s="94" t="s">
+      <c r="C84" s="106">
+        <v>-49.4</v>
+      </c>
+      <c r="D84" s="102">
+        <v>2023</v>
+      </c>
+      <c r="E84" s="103">
+        <v>12</v>
+      </c>
+      <c r="F84" s="104">
+        <v>19</v>
+      </c>
+      <c r="G84" s="99" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B85" s="108" t="s">
         <v>1944</v>
       </c>
-      <c r="C5" s="95">
-        <v>-55.3</v>
-      </c>
-      <c r="D5" s="96">
-        <v>28125</v>
-      </c>
-      <c r="E5" s="101"/>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="106" t="s">
-        <v>1992</v>
-      </c>
-      <c r="B6" s="94" t="s">
+      <c r="C85" s="106">
+        <v>-50</v>
+      </c>
+      <c r="D85" s="102">
+        <v>2023</v>
+      </c>
+      <c r="E85" s="103">
+        <v>12</v>
+      </c>
+      <c r="F85" s="104">
+        <v>20</v>
+      </c>
+      <c r="G85" s="99" t="s">
         <v>1993</v>
       </c>
-      <c r="C6" s="95">
-        <v>-34.200000000000003</v>
-      </c>
-      <c r="D6" s="96">
-        <v>34064</v>
-      </c>
-      <c r="E6" s="101"/>
-    </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="106" t="s">
+    </row>
+    <row r="86" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B86" s="109" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C86" s="106">
+        <v>-48.8</v>
+      </c>
+      <c r="D86" s="102">
+        <v>2024</v>
+      </c>
+      <c r="E86" s="103">
+        <v>1</v>
+      </c>
+      <c r="F86" s="104">
+        <v>21</v>
+      </c>
+      <c r="G86" s="99"/>
+    </row>
+    <row r="87" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B87" s="109" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C87" s="106">
+        <v>-45.6</v>
+      </c>
+      <c r="D87" s="102">
+        <v>2025</v>
+      </c>
+      <c r="E87" s="103">
+        <v>1</v>
+      </c>
+      <c r="F87" s="104">
+        <v>2</v>
+      </c>
+      <c r="G87" s="99" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B88" s="109" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C88" s="106">
+        <v>-45.6</v>
+      </c>
+      <c r="D88" s="102">
+        <v>2025</v>
+      </c>
+      <c r="E88" s="103">
+        <v>1</v>
+      </c>
+      <c r="F88" s="104">
+        <v>16</v>
+      </c>
+      <c r="G88" s="99"/>
+    </row>
+    <row r="89" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="107" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B89" s="108" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C89" s="106">
+        <v>-44.2</v>
+      </c>
+      <c r="D89" s="102">
+        <v>2025</v>
+      </c>
+      <c r="E89" s="103">
+        <v>1</v>
+      </c>
+      <c r="F89" s="104">
+        <v>16</v>
+      </c>
+      <c r="G89" s="101" t="s">
         <v>1994</v>
       </c>
-      <c r="B7" s="94" t="s">
-        <v>1995</v>
-      </c>
-      <c r="C7" s="95">
-        <v>-34.200000000000003</v>
-      </c>
-      <c r="D7" s="96">
-        <v>34065</v>
-      </c>
-      <c r="E7" s="101"/>
-    </row>
-    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="106" t="s">
-        <v>1992</v>
-      </c>
-      <c r="B8" s="94" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C8" s="95">
-        <v>-34</v>
-      </c>
-      <c r="D8" s="96">
-        <v>34066</v>
-      </c>
-      <c r="E8" s="101"/>
-    </row>
-    <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="106" t="s">
-        <v>1992</v>
-      </c>
-      <c r="B9" s="94" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C9" s="95">
-        <v>-30</v>
-      </c>
-      <c r="D9" s="96">
-        <v>34067</v>
-      </c>
-      <c r="E9" s="101"/>
-    </row>
-    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="106" t="s">
-        <v>1988</v>
-      </c>
-      <c r="B10" s="94" t="s">
-        <v>1862</v>
-      </c>
-      <c r="C10" s="95">
-        <v>-30.2</v>
-      </c>
-      <c r="D10" s="96">
-        <v>35162</v>
-      </c>
-      <c r="E10" s="101"/>
-    </row>
-    <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="106" t="s">
-        <v>1988</v>
-      </c>
-      <c r="B11" s="94" t="s">
-        <v>1862</v>
-      </c>
-      <c r="C11" s="95">
-        <v>-50.4</v>
-      </c>
-      <c r="D11" s="96">
-        <v>36531</v>
-      </c>
-      <c r="E11" s="101"/>
-    </row>
-    <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B12" s="94" t="s">
-        <v>1971</v>
-      </c>
-      <c r="C12" s="95">
-        <v>-50</v>
-      </c>
-      <c r="D12" s="96">
-        <v>36899</v>
-      </c>
-      <c r="E12" s="101"/>
-    </row>
-    <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B13" s="94" t="s">
+    </row>
+    <row r="90" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B90" s="109" t="s">
         <v>1791</v>
       </c>
-      <c r="C13" s="95">
-        <v>-50</v>
-      </c>
-      <c r="D13" s="96">
-        <v>38389</v>
-      </c>
-      <c r="E13" s="101"/>
-    </row>
-    <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B14" s="94" t="s">
+      <c r="C90" s="106">
+        <v>-51.2</v>
+      </c>
+      <c r="D90" s="102">
+        <v>2026</v>
+      </c>
+      <c r="E90" s="103">
+        <v>1</v>
+      </c>
+      <c r="F90" s="104">
+        <v>17</v>
+      </c>
+      <c r="G90" s="99"/>
+    </row>
+    <row r="91" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="107" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B91" s="109" t="s">
         <v>1791</v>
       </c>
-      <c r="C14" s="95">
-        <v>-50</v>
-      </c>
-      <c r="D14" s="96">
-        <v>38390</v>
-      </c>
-      <c r="E14" s="101"/>
-    </row>
-    <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B15" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C15" s="95">
-        <v>-50.1</v>
-      </c>
-      <c r="D15" s="96">
-        <v>38391</v>
-      </c>
-      <c r="E15" s="101"/>
-    </row>
-    <row r="16" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B16" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C16" s="95">
-        <v>-50.5</v>
-      </c>
-      <c r="D16" s="96">
-        <v>38392</v>
-      </c>
-      <c r="E16" s="101"/>
-    </row>
-    <row r="17" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B17" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C17" s="95">
-        <v>-49.7</v>
-      </c>
-      <c r="D17" s="96">
-        <v>38393</v>
-      </c>
-      <c r="E17" s="101"/>
-    </row>
-    <row r="18" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B18" s="94" t="s">
-        <v>1979</v>
-      </c>
-      <c r="C18" s="95">
-        <v>-50.5</v>
-      </c>
-      <c r="D18" s="96">
-        <v>38401</v>
-      </c>
-      <c r="E18" s="101"/>
-    </row>
-    <row r="19" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B19" s="94" t="s">
-        <v>1980</v>
-      </c>
-      <c r="C19" s="95">
-        <v>-50.4</v>
-      </c>
-      <c r="D19" s="96">
-        <v>38401</v>
-      </c>
-      <c r="E19" s="101"/>
-    </row>
-    <row r="20" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B20" s="94" t="s">
-        <v>1985</v>
-      </c>
-      <c r="C20" s="95">
-        <v>-40</v>
-      </c>
-      <c r="D20" s="96">
-        <v>38428</v>
-      </c>
-      <c r="E20" s="101"/>
-    </row>
-    <row r="21" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B21" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C21" s="95">
-        <v>-53.8</v>
-      </c>
-      <c r="D21" s="96">
-        <v>38721</v>
-      </c>
-      <c r="E21" s="101"/>
-    </row>
-    <row r="22" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B22" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C22" s="95">
-        <v>-54</v>
-      </c>
-      <c r="D22" s="96">
-        <v>38722</v>
-      </c>
-      <c r="E22" s="101"/>
-    </row>
-    <row r="23" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B23" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C23" s="95">
-        <v>-52.1</v>
-      </c>
-      <c r="D23" s="96">
-        <v>38723</v>
-      </c>
-      <c r="E23" s="101"/>
-    </row>
-    <row r="24" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B24" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C24" s="95">
-        <v>-50.2</v>
-      </c>
-      <c r="D24" s="96">
-        <v>39480</v>
-      </c>
-      <c r="E24" s="101"/>
-    </row>
-    <row r="25" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B25" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C25" s="95">
-        <v>-50</v>
-      </c>
-      <c r="D25" s="96">
-        <v>40221</v>
-      </c>
-      <c r="E25" s="101"/>
-    </row>
-    <row r="26" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B26" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C26" s="95">
-        <v>-49.9</v>
-      </c>
-      <c r="D26" s="96">
-        <v>40223</v>
-      </c>
-      <c r="E26" s="101"/>
-    </row>
-    <row r="27" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="106" t="s">
-        <v>1996</v>
-      </c>
-      <c r="B27" s="94" t="s">
-        <v>1997</v>
-      </c>
-      <c r="C27" s="95">
-        <v>-34.1</v>
-      </c>
-      <c r="D27" s="96">
-        <v>40280</v>
-      </c>
-      <c r="E27" s="101"/>
-    </row>
-    <row r="28" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B28" s="94" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C28" s="95">
-        <v>-50.2</v>
-      </c>
-      <c r="D28" s="96">
-        <v>40563</v>
-      </c>
-      <c r="E28" s="101"/>
-    </row>
-    <row r="29" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="106" t="s">
-        <v>1998</v>
-      </c>
-      <c r="B29" s="94" t="s">
-        <v>1999</v>
-      </c>
-      <c r="C29" s="95">
-        <v>-50.1</v>
-      </c>
-      <c r="D29" s="96">
-        <v>40566</v>
-      </c>
-      <c r="E29" s="101"/>
-    </row>
-    <row r="30" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B30" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C30" s="95">
-        <v>-50.3</v>
-      </c>
-      <c r="D30" s="96">
-        <v>42387</v>
-      </c>
-      <c r="E30" s="101"/>
-    </row>
-    <row r="31" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B31" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C31" s="95">
-        <v>-50.4</v>
-      </c>
-      <c r="D31" s="96">
-        <v>42392</v>
-      </c>
-      <c r="E31" s="101"/>
-    </row>
-    <row r="32" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B32" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C32" s="95">
-        <v>-53.2</v>
-      </c>
-      <c r="D32" s="96">
-        <v>42394</v>
-      </c>
-      <c r="E32" s="101"/>
-    </row>
-    <row r="33" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B33" s="94" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C33" s="95">
-        <v>-50</v>
-      </c>
-      <c r="D33" s="96">
-        <v>42394</v>
-      </c>
-      <c r="E33" s="101"/>
-    </row>
-    <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B34" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C34" s="95">
-        <v>-53</v>
-      </c>
-      <c r="D34" s="96">
-        <v>42395</v>
-      </c>
-      <c r="E34" s="101"/>
-    </row>
-    <row r="35" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B35" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C35" s="95">
-        <v>-53.9</v>
-      </c>
-      <c r="D35" s="96">
-        <v>42396</v>
-      </c>
-      <c r="E35" s="101"/>
-    </row>
-    <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B36" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C36" s="95">
-        <v>-55.3</v>
-      </c>
-      <c r="D36" s="96">
-        <v>42397</v>
-      </c>
-      <c r="E36" s="101"/>
-    </row>
-    <row r="37" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B37" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C37" s="95">
-        <v>-54.4</v>
-      </c>
-      <c r="D37" s="96">
-        <v>42398</v>
-      </c>
-      <c r="E37" s="101"/>
-    </row>
-    <row r="38" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B38" s="94" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C38" s="95">
-        <v>-51.9</v>
-      </c>
-      <c r="D38" s="96">
-        <v>42398</v>
-      </c>
-      <c r="E38" s="101"/>
-    </row>
-    <row r="39" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B39" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C39" s="95">
-        <v>-50.2</v>
-      </c>
-      <c r="D39" s="96">
-        <v>42398</v>
-      </c>
-      <c r="E39" s="101"/>
-    </row>
-    <row r="40" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B40" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C40" s="95">
-        <v>-55</v>
-      </c>
-      <c r="D40" s="96">
-        <v>42399</v>
-      </c>
-      <c r="E40" s="101"/>
-    </row>
-    <row r="41" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B41" s="94" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C41" s="95">
-        <v>-52.8</v>
-      </c>
-      <c r="D41" s="96">
-        <v>42399</v>
-      </c>
-      <c r="E41" s="101"/>
-    </row>
-    <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B42" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C42" s="95">
-        <v>-50.7</v>
-      </c>
-      <c r="D42" s="96">
-        <v>42399</v>
-      </c>
-      <c r="E42" s="101"/>
-    </row>
-    <row r="43" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B43" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C43" s="95">
-        <v>-51.6</v>
-      </c>
-      <c r="D43" s="96">
-        <v>42400</v>
-      </c>
-      <c r="E43" s="101"/>
-    </row>
-    <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B44" s="94" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C44" s="95">
-        <v>-51.5</v>
-      </c>
-      <c r="D44" s="96">
-        <v>42400</v>
-      </c>
-      <c r="E44" s="101"/>
-    </row>
-    <row r="45" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B45" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C45" s="95">
-        <v>-50.5</v>
-      </c>
-      <c r="D45" s="96">
-        <v>42401</v>
-      </c>
-      <c r="E45" s="101"/>
-    </row>
-    <row r="46" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B46" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C46" s="95">
-        <v>-50.2</v>
-      </c>
-      <c r="D46" s="96">
-        <v>42403</v>
-      </c>
-      <c r="E46" s="101"/>
-    </row>
-    <row r="47" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B47" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C47" s="95">
-        <v>-53.2</v>
-      </c>
-      <c r="D47" s="96">
-        <v>42404</v>
-      </c>
-      <c r="E47" s="101"/>
-    </row>
-    <row r="48" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B48" s="94" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C48" s="95">
-        <v>-51</v>
-      </c>
-      <c r="D48" s="96">
-        <v>42404</v>
-      </c>
-      <c r="E48" s="101"/>
-    </row>
-    <row r="49" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B49" s="94" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C49" s="95">
-        <v>-52.9</v>
-      </c>
-      <c r="D49" s="96">
-        <v>42405</v>
-      </c>
-      <c r="E49" s="101"/>
-    </row>
-    <row r="50" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B50" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C50" s="95">
-        <v>-52.3</v>
-      </c>
-      <c r="D50" s="96">
-        <v>42405</v>
-      </c>
-      <c r="E50" s="101"/>
-    </row>
-    <row r="51" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B51" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C51" s="95">
-        <v>-53.3</v>
-      </c>
-      <c r="D51" s="96">
-        <v>42406</v>
-      </c>
-      <c r="E51" s="101"/>
-    </row>
-    <row r="52" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B52" s="94" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C52" s="95">
+      <c r="C91" s="106">
         <v>-52</v>
       </c>
-      <c r="D52" s="96">
-        <v>42406</v>
-      </c>
-      <c r="E52" s="101"/>
-    </row>
-    <row r="53" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B53" s="94" t="s">
-        <v>1787</v>
-      </c>
-      <c r="C53" s="95">
-        <v>-54.7</v>
-      </c>
-      <c r="D53" s="96">
-        <v>42412</v>
-      </c>
-      <c r="E53" s="100"/>
-    </row>
-    <row r="54" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B54" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C54" s="95">
-        <v>-53</v>
-      </c>
-      <c r="D54" s="96">
-        <v>42413</v>
-      </c>
-      <c r="E54" s="100"/>
-    </row>
-    <row r="55" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B55" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C55" s="95">
-        <v>-54.2</v>
-      </c>
-      <c r="D55" s="96">
-        <v>42414</v>
-      </c>
-      <c r="E55" s="100"/>
-    </row>
-    <row r="56" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B56" s="94" t="s">
-        <v>1978</v>
-      </c>
-      <c r="C56" s="95">
-        <v>-50</v>
-      </c>
-      <c r="D56" s="96">
-        <v>42415</v>
-      </c>
-      <c r="E56" s="100"/>
-    </row>
-    <row r="57" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B57" s="94" t="s">
+      <c r="D91" s="102">
+        <v>2026</v>
+      </c>
+      <c r="E91" s="103">
+        <v>1</v>
+      </c>
+      <c r="F91" s="104">
+        <v>18</v>
+      </c>
+      <c r="G91" s="99"/>
+    </row>
+    <row r="92" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="107" t="s">
         <v>1981</v>
       </c>
-      <c r="C57" s="95">
-        <v>-50.2</v>
-      </c>
-      <c r="D57" s="96">
-        <v>42422</v>
-      </c>
-      <c r="E57" s="100"/>
-    </row>
-    <row r="58" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B58" s="94" t="s">
-        <v>1982</v>
-      </c>
-      <c r="C58" s="95">
-        <v>-51.9</v>
-      </c>
-      <c r="D58" s="96">
-        <v>42423</v>
-      </c>
-      <c r="E58" s="100"/>
-    </row>
-    <row r="59" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B59" s="94" t="s">
-        <v>1983</v>
-      </c>
-      <c r="C59" s="95">
-        <v>-50</v>
-      </c>
-      <c r="D59" s="96">
-        <v>42436</v>
-      </c>
-      <c r="E59" s="100"/>
-    </row>
-    <row r="60" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B60" s="94" t="s">
-        <v>1984</v>
-      </c>
-      <c r="C60" s="95">
-        <v>-47.4</v>
-      </c>
-      <c r="D60" s="96">
-        <v>42436</v>
-      </c>
-      <c r="E60" s="100"/>
-    </row>
-    <row r="61" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B61" s="94" t="s">
-        <v>1787</v>
-      </c>
-      <c r="C61" s="95">
-        <v>-50.8</v>
-      </c>
-      <c r="D61" s="96">
-        <v>42437</v>
-      </c>
-      <c r="E61" s="100"/>
-    </row>
-    <row r="62" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B62" s="94" t="s">
-        <v>1787</v>
-      </c>
-      <c r="C62" s="95">
-        <v>-54.2</v>
-      </c>
-      <c r="D62" s="96">
-        <v>42438</v>
-      </c>
-      <c r="E62" s="100"/>
-    </row>
-    <row r="63" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B63" s="94" t="s">
-        <v>1787</v>
-      </c>
-      <c r="C63" s="95">
-        <v>-53</v>
-      </c>
-      <c r="D63" s="96">
-        <v>42439</v>
-      </c>
-      <c r="E63" s="100"/>
-    </row>
-    <row r="64" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B64" s="94" t="s">
-        <v>1788</v>
-      </c>
-      <c r="C64" s="95">
-        <v>-45.4</v>
-      </c>
-      <c r="D64" s="96">
-        <v>42763</v>
-      </c>
-      <c r="E64" s="100"/>
-    </row>
-    <row r="65" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B65" s="94" t="s">
-        <v>1787</v>
-      </c>
-      <c r="C65" s="95">
-        <v>-51.6</v>
-      </c>
-      <c r="D65" s="96">
-        <v>43123</v>
-      </c>
-      <c r="E65" s="100"/>
-    </row>
-    <row r="66" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B66" s="94" t="s">
+      <c r="B92" s="109" t="s">
         <v>1864</v>
       </c>
-      <c r="C66" s="95">
-        <v>-51.3</v>
-      </c>
-      <c r="D66" s="96">
-        <v>43123</v>
-      </c>
-      <c r="E66" s="100"/>
-    </row>
-    <row r="67" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B67" s="94" t="s">
-        <v>1787</v>
-      </c>
-      <c r="C67" s="95">
-        <v>-53.2</v>
-      </c>
-      <c r="D67" s="96">
-        <v>43124</v>
-      </c>
-      <c r="E67" s="100"/>
-    </row>
-    <row r="68" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B68" s="94" t="s">
-        <v>1864</v>
-      </c>
-      <c r="C68" s="95">
-        <v>-51.7</v>
-      </c>
-      <c r="D68" s="96">
-        <v>43124</v>
-      </c>
-      <c r="E68" s="100"/>
-    </row>
-    <row r="69" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B69" s="94" t="s">
-        <v>1864</v>
-      </c>
-      <c r="C69" s="95">
-        <v>-50.7</v>
-      </c>
-      <c r="D69" s="96">
-        <v>43125</v>
-      </c>
-      <c r="E69" s="100"/>
-    </row>
-    <row r="70" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B70" s="94" t="s">
-        <v>1971</v>
-      </c>
-      <c r="C70" s="95">
-        <v>-50.3</v>
-      </c>
-      <c r="D70" s="96">
-        <v>43125</v>
-      </c>
-      <c r="E70" s="100"/>
-    </row>
-    <row r="71" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B71" s="94" t="s">
-        <v>1787</v>
-      </c>
-      <c r="C71" s="95">
-        <v>-50.1</v>
-      </c>
-      <c r="D71" s="96">
-        <v>43125</v>
-      </c>
-      <c r="E71" s="100"/>
-    </row>
-    <row r="72" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B72" s="94" t="s">
-        <v>1864</v>
-      </c>
-      <c r="C72" s="95">
-        <v>-50.2</v>
-      </c>
-      <c r="D72" s="96">
-        <v>43126</v>
-      </c>
-      <c r="E72" s="100" t="s">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B73" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C73" s="95">
-        <v>-49.9</v>
-      </c>
-      <c r="D73" s="96">
-        <v>43126</v>
-      </c>
-      <c r="E73" s="100"/>
-    </row>
-    <row r="74" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B74" s="94" t="s">
-        <v>1789</v>
-      </c>
-      <c r="C74" s="95">
-        <v>-51.8</v>
-      </c>
-      <c r="D74" s="96">
-        <v>43127</v>
-      </c>
-      <c r="E74" s="100"/>
-    </row>
-    <row r="75" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B75" s="94" t="s">
-        <v>1789</v>
-      </c>
-      <c r="C75" s="95">
-        <v>-48.4</v>
-      </c>
-      <c r="D75" s="96">
-        <v>43828</v>
-      </c>
-      <c r="E75" s="100"/>
-    </row>
-    <row r="76" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B76" s="94" t="s">
-        <v>1783</v>
-      </c>
-      <c r="C76" s="95">
-        <v>-49.6</v>
-      </c>
-      <c r="D76" s="96">
-        <v>44194</v>
-      </c>
-      <c r="E76" s="100"/>
-    </row>
-    <row r="77" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B77" s="94" t="s">
-        <v>1783</v>
-      </c>
-      <c r="C77" s="95">
-        <v>-47.2</v>
-      </c>
-      <c r="D77" s="96">
-        <v>44200</v>
-      </c>
-      <c r="E77" s="100"/>
-    </row>
-    <row r="78" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B78" s="94" t="s">
-        <v>1864</v>
-      </c>
-      <c r="C78" s="95">
-        <v>-50</v>
-      </c>
-      <c r="D78" s="96">
-        <v>44949</v>
-      </c>
-      <c r="E78" s="100" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B79" s="94" t="s">
-        <v>1944</v>
-      </c>
-      <c r="C79" s="95">
-        <v>-49.4</v>
-      </c>
-      <c r="D79" s="96">
-        <v>45279</v>
-      </c>
-      <c r="E79" s="100" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B80" s="94" t="s">
-        <v>1944</v>
-      </c>
-      <c r="C80" s="97">
-        <v>-50</v>
-      </c>
-      <c r="D80" s="96">
-        <v>45280</v>
-      </c>
-      <c r="E80" s="100" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B81" s="94" t="s">
-        <v>1783</v>
-      </c>
-      <c r="C81" s="95">
-        <v>-48.8</v>
-      </c>
-      <c r="D81" s="96">
-        <v>45312</v>
-      </c>
-      <c r="E81" s="100"/>
-    </row>
-    <row r="82" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B82" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C82" s="95">
-        <v>-45.6</v>
-      </c>
-      <c r="D82" s="96">
-        <v>45659</v>
-      </c>
-      <c r="E82" s="100" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B83" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C83" s="95">
-        <v>-45.6</v>
-      </c>
-      <c r="D83" s="96">
-        <v>45673</v>
-      </c>
-      <c r="E83" s="100" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B84" s="94" t="s">
-        <v>1790</v>
-      </c>
-      <c r="C84" s="95">
-        <v>-44.2</v>
-      </c>
-      <c r="D84" s="96">
-        <v>45673</v>
-      </c>
-      <c r="E84" s="103" t="s">
-        <v>1968</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B85" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C85" s="95">
-        <v>-51.2</v>
-      </c>
-      <c r="D85" s="98">
-        <v>46039</v>
-      </c>
-      <c r="E85" s="100" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B86" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C86" s="95">
-        <v>-52</v>
-      </c>
-      <c r="D86" s="98">
-        <v>46040</v>
-      </c>
-      <c r="E86" s="100" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B87" s="94" t="s">
-        <v>1864</v>
-      </c>
-      <c r="C87" s="95">
+      <c r="C92" s="106">
         <v>-51.1</v>
       </c>
-      <c r="D87" s="98">
-        <v>46040</v>
-      </c>
-      <c r="E87" s="100" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B88" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C88" s="95">
-        <v>-50</v>
-      </c>
-      <c r="D88" s="96" t="s">
-        <v>1990</v>
-      </c>
-      <c r="E88" s="100"/>
-    </row>
-    <row r="89" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B89" s="94" t="s">
-        <v>1966</v>
-      </c>
-      <c r="C89" s="95">
-        <v>-50</v>
-      </c>
-      <c r="D89" s="96" t="s">
-        <v>1990</v>
-      </c>
-      <c r="E89" s="100"/>
-    </row>
-    <row r="90" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B90" s="94" t="s">
-        <v>1967</v>
-      </c>
-      <c r="C90" s="95">
-        <v>-50</v>
-      </c>
-      <c r="D90" s="96" t="s">
-        <v>1990</v>
-      </c>
-      <c r="E90" s="100"/>
-    </row>
-    <row r="91" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="106" t="s">
-        <v>1986</v>
-      </c>
-      <c r="B91" s="94" t="s">
-        <v>1791</v>
-      </c>
-      <c r="C91" s="95">
-        <v>-50</v>
-      </c>
-      <c r="D91" s="96" t="s">
-        <v>1969</v>
-      </c>
-      <c r="E91" s="100"/>
-    </row>
-    <row r="92" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="106" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B92" s="94" t="s">
-        <v>1784</v>
-      </c>
-      <c r="C92" s="95">
-        <v>-46.8</v>
-      </c>
-      <c r="D92" s="96" t="s">
-        <v>1991</v>
-      </c>
-      <c r="E92" s="100"/>
+      <c r="D92" s="102">
+        <v>2026</v>
+      </c>
+      <c r="E92" s="103">
+        <v>1</v>
+      </c>
+      <c r="F92" s="104">
+        <v>18</v>
+      </c>
+      <c r="G92" s="99"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E92" xr:uid="{94ABDC8A-163A-480F-B2C9-0CD0B852C7D7}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E92">
+  <autoFilter ref="A2:G92" xr:uid="{94ABDC8A-163A-480F-B2C9-0CD0B852C7D7}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G92">
       <sortCondition ref="D2:D92"/>
     </sortState>
   </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C92">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
         <color rgb="FFF72585"/>
-        <color rgb="FFB5179E"/>
-        <color rgb="FF7209B7"/>
+        <color rgb="FF3A0CA3"/>
+        <color rgb="FF4CC9F0"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -33345,12 +33883,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="121" t="s">
         <v>1831</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
     </row>
     <row r="2" spans="1:4" s="27" customFormat="1" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="50" t="s">
@@ -33646,29 +34184,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="122" t="s">
         <v>1941</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
     </row>
     <row r="2" spans="1:11" s="27" customFormat="1" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="127" t="s">
         <v>1775</v>
       </c>
-      <c r="B2" s="121"/>
-      <c r="C2" s="116" t="s">
+      <c r="B2" s="128"/>
+      <c r="C2" s="123" t="s">
         <v>1850</v>
       </c>
-      <c r="D2" s="117"/>
-      <c r="E2" s="118" t="s">
+      <c r="D2" s="124"/>
+      <c r="E2" s="125" t="s">
         <v>1940</v>
       </c>
-      <c r="F2" s="119"/>
+      <c r="F2" s="126"/>
       <c r="G2" s="51" t="s">
         <v>1942</v>
       </c>
@@ -34750,32 +35288,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="1.2">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="129" t="s">
         <v>1964</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
     </row>
     <row r="2" spans="1:11" s="27" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="124" t="s">
+      <c r="A2" s="131" t="s">
         <v>1775</v>
       </c>
-      <c r="B2" s="124"/>
+      <c r="B2" s="131"/>
       <c r="C2" s="84" t="s">
         <v>1960</v>
       </c>
-      <c r="D2" s="125" t="s">
+      <c r="D2" s="132" t="s">
         <v>1965</v>
       </c>
-      <c r="E2" s="126"/>
-      <c r="F2" s="127" t="s">
+      <c r="E2" s="133"/>
+      <c r="F2" s="134" t="s">
         <v>1963</v>
       </c>
-      <c r="G2" s="128"/>
+      <c r="G2" s="135"/>
     </row>
     <row r="3" spans="1:11" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="57" t="s">

--- a/气象/蒙古气象/蒙古低温收集 & 东亚极端冷月均温排名.xlsx
+++ b/气象/蒙古气象/蒙古低温收集 & 东亚极端冷月均温排名.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\蒙古气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D420923-6D49-406E-BC90-1EFC6AAC0AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDF8ADD-FFD0-499D-8F35-0ED9B6BBC9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{237916A9-0E72-4A8C-88B8-0F539FC0B012}"/>
   </bookViews>
